--- a/GameConfig/Datas/关卡/怪物配置表.xlsx
+++ b/GameConfig/Datas/关卡/怪物配置表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\关卡\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD08683-B5C7-4FAD-B878-66A9A5A0EB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="怪物配置表" sheetId="14" r:id="rId1"/>
@@ -14,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">怪物配置表!$B$5:$BB$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">怪物配置表!$B$5:$BC$6</definedName>
     <definedName name="地窟攻击">#REF!</definedName>
     <definedName name="地窟伤害减免">#REF!</definedName>
     <definedName name="地窟生命">#REF!</definedName>
@@ -51,18 +57,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>dmlt</author>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="B5" authorId="0">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>ID规范：</t>
@@ -72,6 +79,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -81,6 +89,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -91,6 +100,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>xxx</t>
@@ -99,6 +109,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">-玩法 1X-主线（X序号） 99-测试
@@ -109,6 +120,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>y-</t>
@@ -117,6 +129,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">怪物分类 1-小怪  2-精英 3-BOSS
@@ -127,6 +140,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>zzz-</t>
@@ -135,19 +149,21 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>怪物序号</t>
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="1">
+    <comment ref="H5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -156,6 +172,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -168,25 +185,27 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0">
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>目前只在召唤有用</t>
         </r>
       </text>
     </comment>
-    <comment ref="Q5" authorId="0">
+    <comment ref="R5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>dmlt:</t>
@@ -195,6 +214,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -203,13 +223,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0">
+    <comment ref="T5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>dmlt:</t>
@@ -218,6 +239,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -227,13 +249,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y5" authorId="0">
+    <comment ref="Z5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">不知道这个有没有用？？？？
@@ -243,6 +266,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -255,7 +279,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="93">
   <si>
     <t>##var</t>
   </si>
@@ -365,182 +389,186 @@
     <t>模型ID</t>
   </si>
   <si>
+    <t>关卡名称</t>
+  </si>
+  <si>
+    <t>属性角标</t>
+  </si>
+  <si>
+    <t>怪物类型</t>
+  </si>
+  <si>
+    <t>模型缩放倍率</t>
+  </si>
+  <si>
+    <t>死亡消失时间</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>模板类型</t>
+  </si>
+  <si>
+    <t>模板说明</t>
+  </si>
+  <si>
+    <t>怪物攻击倍率</t>
+  </si>
+  <si>
+    <t>是否远程小怪</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>怪物血量倍率</t>
+  </si>
+  <si>
+    <t>血量</t>
+  </si>
+  <si>
+    <t>是否显示头顶血条</t>
+  </si>
+  <si>
+    <t>血条数量</t>
+  </si>
+  <si>
+    <t>怪物血量_制表用</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>经验</t>
+  </si>
+  <si>
+    <t>掉落ID</t>
+  </si>
+  <si>
+    <t>伤害减免</t>
+  </si>
+  <si>
+    <t>怪物血条长度系数</t>
+  </si>
+  <si>
+    <t>初始属性_1_ID</t>
+  </si>
+  <si>
+    <t>初始属性_1_类型</t>
+  </si>
+  <si>
+    <t>初始属性_1_数值</t>
+  </si>
+  <si>
+    <t>初始属性_2_ID</t>
+  </si>
+  <si>
+    <t>初始属性_2_类型</t>
+  </si>
+  <si>
+    <t>初始属性_2_数值</t>
+  </si>
+  <si>
+    <t>初始属性_3_ID</t>
+  </si>
+  <si>
+    <t>初始属性_3_类型</t>
+  </si>
+  <si>
+    <t>初始属性_3_数值</t>
+  </si>
+  <si>
+    <t>初始属性_4_ID</t>
+  </si>
+  <si>
+    <t>初始属性_4_类型</t>
+  </si>
+  <si>
+    <t>初始属性_4_数值</t>
+  </si>
+  <si>
+    <t>初始属性_5_ID</t>
+  </si>
+  <si>
+    <t>初始属性_5_类型</t>
+  </si>
+  <si>
+    <t>初始属性_5_数值</t>
+  </si>
+  <si>
+    <t>初始属性_6_ID</t>
+  </si>
+  <si>
+    <t>初始属性_6_类型</t>
+  </si>
+  <si>
+    <t>初始属性_6_数值</t>
+  </si>
+  <si>
+    <t>初始属性_7_ID</t>
+  </si>
+  <si>
+    <t>初始属性_7_类型</t>
+  </si>
+  <si>
+    <t>初始属性_7_数值</t>
+  </si>
+  <si>
+    <t>技能_1</t>
+  </si>
+  <si>
+    <t>技能_2</t>
+  </si>
+  <si>
+    <t>技能_3</t>
+  </si>
+  <si>
+    <t>技能_4</t>
+  </si>
+  <si>
+    <t>技能_5</t>
+  </si>
+  <si>
+    <t>附身技能</t>
+  </si>
+  <si>
+    <t>循环播放技能</t>
+  </si>
+  <si>
+    <t>AI行为ID</t>
+  </si>
+  <si>
+    <t>描边大小</t>
+  </si>
+  <si>
+    <t>描边颜色</t>
+  </si>
+  <si>
+    <t>bf4646</t>
+  </si>
+  <si>
+    <t>史莱姆</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterNameId</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
     <t>模型名称</t>
-  </si>
-  <si>
-    <t>关卡名称</t>
-  </si>
-  <si>
-    <t>属性角标</t>
-  </si>
-  <si>
-    <t>怪物类型</t>
-  </si>
-  <si>
-    <t>模型缩放倍率</t>
-  </si>
-  <si>
-    <t>死亡消失时间</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>模板类型</t>
-  </si>
-  <si>
-    <t>模板说明</t>
-  </si>
-  <si>
-    <t>怪物攻击倍率</t>
-  </si>
-  <si>
-    <t>是否远程小怪</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>怪物血量倍率</t>
-  </si>
-  <si>
-    <t>血量</t>
-  </si>
-  <si>
-    <t>是否显示头顶血条</t>
-  </si>
-  <si>
-    <t>血条数量</t>
-  </si>
-  <si>
-    <t>怪物血量_制表用</t>
-  </si>
-  <si>
-    <t>移动速度</t>
-  </si>
-  <si>
-    <t>经验</t>
-  </si>
-  <si>
-    <t>掉落ID</t>
-  </si>
-  <si>
-    <t>伤害减免</t>
-  </si>
-  <si>
-    <t>怪物血条长度系数</t>
-  </si>
-  <si>
-    <t>初始属性_1_ID</t>
-  </si>
-  <si>
-    <t>初始属性_1_类型</t>
-  </si>
-  <si>
-    <t>初始属性_1_数值</t>
-  </si>
-  <si>
-    <t>初始属性_2_ID</t>
-  </si>
-  <si>
-    <t>初始属性_2_类型</t>
-  </si>
-  <si>
-    <t>初始属性_2_数值</t>
-  </si>
-  <si>
-    <t>初始属性_3_ID</t>
-  </si>
-  <si>
-    <t>初始属性_3_类型</t>
-  </si>
-  <si>
-    <t>初始属性_3_数值</t>
-  </si>
-  <si>
-    <t>初始属性_4_ID</t>
-  </si>
-  <si>
-    <t>初始属性_4_类型</t>
-  </si>
-  <si>
-    <t>初始属性_4_数值</t>
-  </si>
-  <si>
-    <t>初始属性_5_ID</t>
-  </si>
-  <si>
-    <t>初始属性_5_类型</t>
-  </si>
-  <si>
-    <t>初始属性_5_数值</t>
-  </si>
-  <si>
-    <t>初始属性_6_ID</t>
-  </si>
-  <si>
-    <t>初始属性_6_类型</t>
-  </si>
-  <si>
-    <t>初始属性_6_数值</t>
-  </si>
-  <si>
-    <t>初始属性_7_ID</t>
-  </si>
-  <si>
-    <t>初始属性_7_类型</t>
-  </si>
-  <si>
-    <t>初始属性_7_数值</t>
-  </si>
-  <si>
-    <t>技能_1</t>
-  </si>
-  <si>
-    <t>技能_2</t>
-  </si>
-  <si>
-    <t>技能_3</t>
-  </si>
-  <si>
-    <t>技能_4</t>
-  </si>
-  <si>
-    <t>技能_5</t>
-  </si>
-  <si>
-    <t>附身技能</t>
-  </si>
-  <si>
-    <t>循环播放技能</t>
-  </si>
-  <si>
-    <t>AI行为ID</t>
-  </si>
-  <si>
-    <t>描边大小</t>
-  </si>
-  <si>
-    <t>描边颜色</t>
-  </si>
-  <si>
-    <t>史莱姆</t>
-  </si>
-  <si>
-    <t>bf4646</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -552,12 +580,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -565,6 +595,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -573,170 +604,61 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -769,13 +691,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -785,164 +707,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -967,29 +733,29 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1008,253 +774,32 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="52">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1272,62 +817,52 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="52">
+  <cellStyles count="6">
+    <cellStyle name="差" xfId="2" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 7" xfId="50"/>
-    <cellStyle name="注释 2" xfId="51"/>
+    <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 7" xfId="4" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="注释 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1342,19 +877,22 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
-      <color rgb="00FFFFCC"/>
+      <color rgb="FFFFFFCC"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="怪物配置表"/>
@@ -1375,7 +913,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="怪物配置表"/>
@@ -1676,67 +1214,69 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
-    <tabColor theme="3" tint="0.599993896298105"/>
+    <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:BD6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="5"/>
+  <dimension ref="A1:BE6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="12.2166666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="20.9666666666667" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.125" style="1" customWidth="1"/>
-    <col min="15" max="16" width="8.625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10.375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.25" style="1" customWidth="1"/>
-    <col min="21" max="21" width="10.375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="8.375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="11.5" style="1" customWidth="1"/>
-    <col min="24" max="24" width="17.125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="14.875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="13.3333333333333" style="1" customWidth="1"/>
-    <col min="27" max="27" width="18.4666666666667" style="1" customWidth="1"/>
-    <col min="28" max="28" width="16.6583333333333" style="1" customWidth="1"/>
-    <col min="29" max="29" width="21.25" style="1" customWidth="1"/>
-    <col min="30" max="30" width="18.6083333333333" style="1" customWidth="1"/>
-    <col min="31" max="31" width="15.9666666666667" style="1" customWidth="1"/>
-    <col min="32" max="32" width="17.3666666666667" style="1" customWidth="1"/>
-    <col min="33" max="33" width="15.55" style="1" customWidth="1"/>
-    <col min="34" max="34" width="15.975" style="1" customWidth="1"/>
-    <col min="35" max="35" width="18.8833333333333" style="1" customWidth="1"/>
-    <col min="36" max="36" width="17.6333333333333" style="1" customWidth="1"/>
-    <col min="37" max="37" width="15.8333333333333" style="1" customWidth="1"/>
-    <col min="38" max="38" width="18.8916666666667" style="1" customWidth="1"/>
-    <col min="39" max="39" width="17.3583333333333" style="1" customWidth="1"/>
-    <col min="40" max="40" width="15.55" style="1" customWidth="1"/>
-    <col min="41" max="41" width="14.375" style="1" customWidth="1"/>
-    <col min="42" max="43" width="16.25" style="1" customWidth="1"/>
-    <col min="44" max="44" width="14.375" style="1" customWidth="1"/>
-    <col min="45" max="46" width="16.25" style="1" customWidth="1"/>
-    <col min="47" max="51" width="10.5" style="1" customWidth="1"/>
-    <col min="52" max="52" width="12" style="1" customWidth="1"/>
-    <col min="53" max="53" width="14.875" style="1" customWidth="1"/>
-    <col min="54" max="54" width="9.375" style="1" customWidth="1"/>
-    <col min="55" max="56" width="13.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.90625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.453125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.08984375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6.36328125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.6328125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.08984375" style="1" customWidth="1"/>
+    <col min="16" max="17" width="8.6328125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="10.36328125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="9.36328125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.36328125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="7.26953125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="10.36328125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="8.36328125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="11.453125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="17.08984375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="14.90625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.36328125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="18.453125" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16.6328125" style="1" customWidth="1"/>
+    <col min="30" max="30" width="21.26953125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="18.6328125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="16" style="1" customWidth="1"/>
+    <col min="33" max="33" width="17.36328125" style="1" customWidth="1"/>
+    <col min="34" max="34" width="15.54296875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="16" style="1" customWidth="1"/>
+    <col min="36" max="36" width="18.90625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="17.6328125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="15.81640625" style="1" customWidth="1"/>
+    <col min="39" max="39" width="18.90625" style="1" customWidth="1"/>
+    <col min="40" max="40" width="17.36328125" style="1" customWidth="1"/>
+    <col min="41" max="41" width="15.54296875" style="1" customWidth="1"/>
+    <col min="42" max="42" width="14.36328125" style="1" customWidth="1"/>
+    <col min="43" max="44" width="16.26953125" style="1" customWidth="1"/>
+    <col min="45" max="45" width="14.36328125" style="1" customWidth="1"/>
+    <col min="46" max="47" width="16.26953125" style="1" customWidth="1"/>
+    <col min="48" max="52" width="10.453125" style="1" customWidth="1"/>
+    <col min="53" max="53" width="12" style="1" customWidth="1"/>
+    <col min="54" max="54" width="14.90625" style="1" customWidth="1"/>
+    <col min="55" max="55" width="9.36328125" style="1" customWidth="1"/>
+    <col min="56" max="57" width="13.7265625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" spans="1:56">
+    <row r="1" spans="1:57" ht="14" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1747,28 +1287,28 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>3</v>
@@ -1780,85 +1320,88 @@
         <v>3</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
-      <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
-      <c r="AR1" s="2"/>
-      <c r="AS1" s="2"/>
-      <c r="AT1" s="2"/>
-      <c r="AU1" s="2" t="s">
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
+      <c r="AM1" s="9"/>
+      <c r="AN1" s="9"/>
+      <c r="AO1" s="9"/>
+      <c r="AP1" s="9"/>
+      <c r="AQ1" s="9"/>
+      <c r="AR1" s="9"/>
+      <c r="AS1" s="9"/>
+      <c r="AT1" s="9"/>
+      <c r="AU1" s="9"/>
+      <c r="AV1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="AV1" s="2"/>
-      <c r="AW1" s="2"/>
-      <c r="AX1" s="2"/>
-      <c r="AY1" s="2"/>
-      <c r="AZ1" s="2" t="s">
+      <c r="AW1" s="9"/>
+      <c r="AX1" s="9"/>
+      <c r="AY1" s="9"/>
+      <c r="AZ1" s="9"/>
+      <c r="BA1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BB1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BC1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BD1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BE1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="13.5" spans="1:56">
+    <row r="2" spans="1:57" ht="14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
@@ -1868,47 +1411,47 @@
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>28</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
-      <c r="O2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="S2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3" t="s">
+      <c r="T2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="V2" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W2" s="3" t="s">
         <v>26</v>
       </c>
@@ -1916,41 +1459,41 @@
         <v>26</v>
       </c>
       <c r="Y2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="AA2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="3"/>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="3"/>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="3"/>
-      <c r="AN2" s="3"/>
-      <c r="AO2" s="3"/>
-      <c r="AP2" s="3"/>
-      <c r="AQ2" s="3"/>
-      <c r="AR2" s="3"/>
-      <c r="AS2" s="3"/>
-      <c r="AT2" s="3"/>
-      <c r="AU2" s="3" t="s">
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AG2" s="10"/>
+      <c r="AH2" s="10"/>
+      <c r="AI2" s="10"/>
+      <c r="AJ2" s="10"/>
+      <c r="AK2" s="10"/>
+      <c r="AL2" s="10"/>
+      <c r="AM2" s="10"/>
+      <c r="AN2" s="10"/>
+      <c r="AO2" s="10"/>
+      <c r="AP2" s="10"/>
+      <c r="AQ2" s="10"/>
+      <c r="AR2" s="10"/>
+      <c r="AS2" s="10"/>
+      <c r="AT2" s="10"/>
+      <c r="AU2" s="10"/>
+      <c r="AV2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AV2" s="3"/>
-      <c r="AW2" s="3"/>
-      <c r="AX2" s="3"/>
-      <c r="AY2" s="3"/>
-      <c r="AZ2" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="AW2" s="10"/>
+      <c r="AX2" s="10"/>
+      <c r="AY2" s="10"/>
+      <c r="AZ2" s="10"/>
       <c r="BA2" s="3" t="s">
         <v>26</v>
       </c>
@@ -1961,10 +1504,13 @@
         <v>26</v>
       </c>
       <c r="BD2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="BE2" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" ht="13.5" spans="1:56">
+    <row r="3" spans="1:57" ht="14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -1992,72 +1538,70 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
-      <c r="Z3" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AC3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AC3" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AD3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AF3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AF3" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AG3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AH3" s="3" t="s">
+      <c r="AI3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AI3" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AJ3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AK3" s="3" t="s">
+      <c r="AL3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AL3" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AM3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AN3" s="3" t="s">
+      <c r="AO3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AO3" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AP3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AQ3" s="3" t="s">
+      <c r="AR3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AR3" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AS3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AT3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AT3" s="3" t="s">
+      <c r="AU3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AU3" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AV3" s="3" t="s">
         <v>26</v>
       </c>
@@ -2070,13 +1614,16 @@
       <c r="AY3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AZ3" s="3"/>
+      <c r="AZ3" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="BA3" s="3"/>
       <c r="BB3" s="3"/>
       <c r="BC3" s="3"/>
       <c r="BD3" s="3"/>
+      <c r="BE3" s="3"/>
     </row>
-    <row r="4" ht="13.5" spans="1:56">
+    <row r="4" spans="1:57" ht="14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
@@ -2135,8 +1682,9 @@
       <c r="BB4" s="2"/>
       <c r="BC4" s="2"/>
       <c r="BD4" s="2"/>
+      <c r="BE4" s="2"/>
     </row>
-    <row r="5" ht="33" spans="1:56">
+    <row r="5" spans="1:57" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -2146,167 +1694,170 @@
       <c r="C5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="L5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="O5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="P5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="Q5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="R5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="S5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="T5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="U5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="T5" s="5" t="s">
+      <c r="V5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="W5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="X5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="Y5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="Z5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="AA5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="Z5" s="4" t="s">
+      <c r="AB5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="AA5" s="4" t="s">
+      <c r="AC5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AB5" s="4" t="s">
+      <c r="AD5" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AC5" s="4" t="s">
+      <c r="AE5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AD5" s="4" t="s">
+      <c r="AF5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="AE5" s="4" t="s">
+      <c r="AG5" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="AF5" s="4" t="s">
+      <c r="AH5" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AG5" s="4" t="s">
+      <c r="AI5" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AH5" s="4" t="s">
+      <c r="AJ5" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AI5" s="4" t="s">
+      <c r="AK5" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="AJ5" s="4" t="s">
+      <c r="AL5" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="AK5" s="4" t="s">
+      <c r="AM5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="AL5" s="4" t="s">
+      <c r="AN5" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="AM5" s="4" t="s">
+      <c r="AO5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="AN5" s="4" t="s">
+      <c r="AP5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="AO5" s="4" t="s">
+      <c r="AQ5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="AP5" s="4" t="s">
+      <c r="AR5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="AQ5" s="4" t="s">
+      <c r="AS5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AR5" s="4" t="s">
+      <c r="AT5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AS5" s="4" t="s">
+      <c r="AU5" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="AT5" s="4" t="s">
+      <c r="AV5" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="AU5" s="4" t="s">
+      <c r="AW5" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="AV5" s="4" t="s">
+      <c r="AX5" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="AW5" s="4" t="s">
+      <c r="AY5" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="AX5" s="4" t="s">
+      <c r="AZ5" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="AY5" s="4" t="s">
+      <c r="BA5" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AZ5" s="4" t="s">
+      <c r="BB5" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="BA5" s="4" t="s">
+      <c r="BC5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="BB5" s="4" t="s">
+      <c r="BD5" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="BC5" s="4" t="s">
+      <c r="BE5" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="BD5" s="4" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
       <c r="B6" s="6">
         <v>9001</v>
@@ -2314,15 +1865,15 @@
       <c r="C6" s="6">
         <v>100111</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="6">
+        <v>10300001</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6">
+      <c r="F6" s="6"/>
+      <c r="G6" s="6">
         <v>38</v>
-      </c>
-      <c r="G6" s="7">
-        <v>1</v>
       </c>
       <c r="H6" s="7">
         <v>1</v>
@@ -2334,46 +1885,48 @@
         <v>1</v>
       </c>
       <c r="K6" s="7">
+        <v>1</v>
+      </c>
+      <c r="L6" s="7">
         <v>90000</v>
       </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7">
+      <c r="M6" s="7"/>
+      <c r="N6" s="7">
         <v>1</v>
       </c>
-      <c r="N6" s="7"/>
-      <c r="O6" s="8">
+      <c r="O6" s="7"/>
+      <c r="P6" s="8">
         <v>25</v>
       </c>
-      <c r="P6" s="7">
+      <c r="Q6" s="7">
         <v>1</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="R6" s="7">
         <v>10000</v>
       </c>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7">
+      <c r="S6" s="7"/>
+      <c r="T6" s="7">
         <v>1</v>
       </c>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7">
+      <c r="U6" s="7"/>
+      <c r="V6" s="7">
         <v>0.8</v>
       </c>
-      <c r="V6" s="7">
+      <c r="W6" s="7">
         <v>0</v>
       </c>
-      <c r="W6" s="7"/>
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
-      <c r="Z6" s="7">
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7">
         <v>2</v>
       </c>
-      <c r="AA6" s="7">
+      <c r="AB6" s="7">
         <v>1</v>
       </c>
-      <c r="AB6" s="7">
+      <c r="AC6" s="7">
         <v>10</v>
       </c>
-      <c r="AC6" s="7"/>
       <c r="AD6" s="7"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="7"/>
@@ -2399,31 +1952,32 @@
       <c r="AZ6" s="7"/>
       <c r="BA6" s="7"/>
       <c r="BB6" s="7"/>
-      <c r="BC6" s="7">
+      <c r="BC6" s="7"/>
+      <c r="BD6" s="7">
         <v>0</v>
       </c>
-      <c r="BD6" s="7" t="s">
-        <v>90</v>
+      <c r="BE6" s="7" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="Z1:AT1"/>
-    <mergeCell ref="AU1:AY1"/>
-    <mergeCell ref="Z2:AT2"/>
-    <mergeCell ref="AU2:AY2"/>
+    <mergeCell ref="AA1:AU1"/>
+    <mergeCell ref="AV1:AZ1"/>
+    <mergeCell ref="AA2:AU2"/>
+    <mergeCell ref="AV2:AZ2"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="0" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="15264"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15264"/>
     <cfRule type="duplicateValues" dxfId="0" priority="15270"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>